--- a/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
+++ b/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
@@ -11,14 +11,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="4" width="26" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>gpt-oss extrx: CE vs STD</t>
+          <t>gpt-oss extrx: STD vs CE</t>
         </is>
       </c>
     </row>
@@ -76,6 +76,11 @@
           <t>StarDepth=2</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>StarDepth=3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -95,6 +100,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -120,6 +130,11 @@
           <t>3/3 [##########]; s=48; r=5</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -134,12 +149,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>0/3 [----------]; s=NA; r=NA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -164,6 +184,11 @@
           <t>0/3 [----------]; s=NA; r=NA</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -186,6 +211,11 @@
           <t>0/3 [----------]; s=NA; r=NA</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -208,6 +238,11 @@
           <t>0/3 [----------]; s=NA; r=NA</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -230,6 +265,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -266,6 +306,11 @@
           <t>StarDepth=2</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>StarDepth=3</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -285,6 +330,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>NA</t>
         </is>
       </c>
@@ -310,6 +360,11 @@
           <t>3/3 [##########]; s=11; r=2</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -324,12 +379,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>3/3 [##########]; s=167; r=4</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
     </row>
@@ -354,6 +414,11 @@
           <t>3/3 [##########]; s=1095; r=7</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -376,6 +441,11 @@
           <t>0/3 [----------]; s=NA; r=NA</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -398,6 +468,11 @@
           <t>2/3 [#######---]; s=457; r=3</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -418,6 +493,248 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CE / single_inference</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>#States</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>StarDepth=0</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>StarDepth=1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>StarDepth=2</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>StarDepth=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=9; r=2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=9; r=2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=15; r=2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=15; r=3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=9; r=2</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=70; r=2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=9; r=2</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1/3 [###-------]; s=563; r=12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0/3 [----------]; s=NA; r=NA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>0/3 [----------]; s=NA; r=NA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0/3 [----------]; s=NA; r=NA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=599; r=9</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>3/3 [##########]; s=8; r=1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0/3 [----------]; s=NA; r=NA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
+++ b/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
@@ -100,7 +100,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>3/3 [##########]; s=48; r=5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -149,7 +149,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>3/3 [##########]; s=12; r=3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -330,7 +330,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>3/3 [##########]; s=8; r=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -379,7 +379,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>3/3 [##########]; s=8; r=1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">

--- a/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
+++ b/logs/scaleup/summary/oss_extrx_ce_std_analysis.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=9; r=2</t>
+          <t>3/3 [##########]; s=8; r=1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -577,17 +577,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=15; r=3</t>
+          <t>3/3 [##########]; s=10; r=2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=8; r=1</t>
+          <t>3/3 [##########]; s=16; r=9</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=9; r=2</t>
+          <t>3/3 [##########]; s=12; r=3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=8; r=1</t>
+          <t>3/3 [##########]; s=12; r=2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=70; r=2</t>
+          <t>2/3 [#######---]; s=796.5; r=7.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=9; r=2</t>
+          <t>3/3 [##########]; s=8; r=1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1/3 [###-------]; s=563; r=12</t>
+          <t>1/3 [###-------]; s=371; r=6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=8; r=1</t>
+          <t>3/3 [##########]; s=9; r=2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0/3 [----------]; s=NA; r=NA</t>
+          <t>1/3 [###-------]; s=509; r=9</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3/3 [##########]; s=599; r=9</t>
+          <t>1/3 [###-------]; s=793; r=9</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
